--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_回数日数ベース見込量_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_回数日数ベース見込量_20260914.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_見込量_介護" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_見込量_予防" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_計画書掲載用" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_定員との突合" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_突合結果" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,10 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0％"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +53,10 @@
     </font>
     <font>
       <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -108,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -144,17 +150,17 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -165,10 +171,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -4194,18 +4221,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -4213,7 +4240,10 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4249,72 +4279,87 @@
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
+          <t>R7 単価(円/件)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>見込単価(円/件)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>単価の乖離</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
           <t>9年度 人/月</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>9年度 量/月</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>9年度 給付費(千円)</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>10年度 人/月</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>10年度 量/月</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>10年度 給付費(千円)</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>11年度 人/月</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>11年度 量/月</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>11年度 給付費(千円)</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>R7→R11</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>訪問介護</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>回</t>
         </is>
@@ -4322,47 +4367,58 @@
       <c r="D2" s="8" t="n">
         <v>11.97040498442368</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="13" t="n">
         <v>52.33333333333334</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="13" t="n">
         <v>640.4166666666666</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="G2" s="7" t="n">
+        <v>47368.45222929936</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>40829.54580638403</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>-13.8％</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="n">
         <v>66.6591627718322</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="K2" s="13" t="n">
         <v>797.9371743014493</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="L2" s="7" t="n">
         <v>32659.96007769278</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="M2" s="13" t="n">
         <v>66.46527340949412</v>
       </c>
-      <c r="K2" s="14" t="n">
+      <c r="N2" s="13" t="n">
         <v>795.6162401120908</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="O2" s="7" t="n">
         <v>32564.96310248135</v>
       </c>
-      <c r="M2" s="14" t="n">
+      <c r="P2" s="13" t="n">
         <v>66.27138404715605</v>
       </c>
-      <c r="N2" s="14" t="n">
+      <c r="Q2" s="13" t="n">
         <v>793.2953059227324</v>
       </c>
-      <c r="O2" s="7" t="n">
+      <c r="R2" s="7" t="n">
         <v>32469.96612726991</v>
       </c>
-      <c r="P2" s="13" t="inlineStr">
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>+23.9％</t>
         </is>
       </c>
-      <c r="Q2" s="15" t="inlineStr">
-        <is>
-          <t>**令和7年度実績から15％を超えて動く。基準期間を令和5〜7年度の3年平均としているため、一方向に動いてきたサービスでは平均に引き戻される。00シートの「趨勢のあるサービスの扱い」を参照**</t>
+      <c r="T2" s="9" t="inlineStr">
+        <is>
+          <t>**見込単価が令和7年度実績から10％を超えて離れる。単価も一方向に動いてきたため、3年平均が実績から離れる。件数と単価が逆方向に動くと給付費では打ち消し合う**</t>
         </is>
       </c>
     </row>
@@ -4385,45 +4441,56 @@
       <c r="D3" s="8" t="n">
         <v>3.867647058823529</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="13" t="n">
         <v>5.666666666666667</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="13" t="n">
         <v>21.91666666666667</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="G3" s="7" t="n">
+        <v>46623.72058823529</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>46220.48962172807</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>-0.9％</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="n">
         <v>6.534012965975934</v>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="K3" s="13" t="n">
         <v>25.27125603017163</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="L3" s="7" t="n">
         <v>3624.063341785528</v>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="M3" s="13" t="n">
         <v>6.515007692660123</v>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="N3" s="13" t="n">
         <v>25.19775034072959</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="O3" s="7" t="n">
         <v>3613.522145328909</v>
       </c>
-      <c r="M3" s="14" t="n">
+      <c r="P3" s="13" t="n">
         <v>6.496002419344311</v>
       </c>
-      <c r="N3" s="14" t="n">
+      <c r="Q3" s="13" t="n">
         <v>25.12424465128755</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="R3" s="7" t="n">
         <v>3602.98094887229</v>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>+14.6％</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr"/>
+      <c r="T3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4444,45 +4511,56 @@
       <c r="D4" s="8" t="n">
         <v>4.90057361376673</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="13" t="n">
         <v>43.25</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="13" t="n">
         <v>213.5833333333333</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="7" t="n">
+        <v>38895.64739884393</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>40729.12144399775</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>+4.7％</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="n">
         <v>39.71293630786739</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="K4" s="13" t="n">
         <v>194.6161677955337</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="L4" s="7" t="n">
         <v>19409.67606937054</v>
       </c>
-      <c r="J4" s="14" t="n">
+      <c r="M4" s="13" t="n">
         <v>39.59742456758854</v>
       </c>
-      <c r="K4" s="14" t="n">
+      <c r="N4" s="13" t="n">
         <v>194.0500940090429</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="O4" s="7" t="n">
         <v>19353.21976899424</v>
       </c>
-      <c r="M4" s="14" t="n">
+      <c r="P4" s="13" t="n">
         <v>39.48191282730969</v>
       </c>
-      <c r="N4" s="14" t="n">
+      <c r="Q4" s="13" t="n">
         <v>193.4840202225521</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="R4" s="7" t="n">
         <v>19296.76346861795</v>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>-9.4％</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr"/>
+      <c r="T4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4503,45 +4581,52 @@
       <c r="D5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="14" t="n">
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="14" t="n">
+      <c r="M5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -4564,37 +4649,48 @@
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <v>16.25</v>
       </c>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="14" t="n">
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="7" t="n">
+        <v>4443.502564102564</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>4504.302513368592</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>+1.4％</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="n">
         <v>17.0831491621058</v>
       </c>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="7" t="n">
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="7" t="n">
         <v>923.3720604854846</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="M6" s="13" t="n">
         <v>17.0334599557006</v>
       </c>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="7" t="n">
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="7" t="n">
         <v>920.6862778779062</v>
       </c>
-      <c r="M6" s="14" t="n">
+      <c r="P6" s="13" t="n">
         <v>16.98377074929541</v>
       </c>
-      <c r="N6" s="16" t="n"/>
-      <c r="O6" s="7" t="n">
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="7" t="n">
         <v>918.0004952703275</v>
       </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>+4.5％</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="inlineStr"/>
+      <c r="T6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4615,45 +4711,56 @@
       <c r="D7" s="8" t="n">
         <v>8.799026763990268</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13" t="n">
         <v>171.0833333333333</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="13" t="n">
         <v>1506.833333333333</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="7" t="n">
+        <v>74276.94885533366</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>73698.25456429717</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>-0.8％</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="n">
         <v>177.488762679502</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="K7" s="13" t="n">
         <v>1561.728373124455</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="L7" s="7" t="n">
         <v>156967.3441710728</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="M7" s="13" t="n">
         <v>176.9725068252859</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="N7" s="13" t="n">
         <v>1557.185824046141</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="O7" s="7" t="n">
         <v>156510.7783067008</v>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="P7" s="13" t="n">
         <v>176.4562509710697</v>
       </c>
-      <c r="N7" s="14" t="n">
+      <c r="Q7" s="13" t="n">
         <v>1552.643274967826</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="R7" s="7" t="n">
         <v>156054.2124423289</v>
       </c>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="S7" s="6" t="inlineStr">
         <is>
           <t>+3.0％</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr"/>
+      <c r="T7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4674,45 +4781,56 @@
       <c r="D8" s="8" t="n">
         <v>6.697749196141479</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="13" t="n">
         <v>25.91666666666667</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="13" t="n">
         <v>173.5833333333333</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="7" t="n">
+        <v>50081.88424437299</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>47647.0982112151</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>-4.9％</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="n">
         <v>24.86653798032146</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="K8" s="13" t="n">
         <v>166.5498347685196</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="L8" s="7" t="n">
         <v>14217.82052785544</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="M8" s="13" t="n">
         <v>24.7942094812513</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="N8" s="13" t="n">
         <v>166.0653966220143</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="O8" s="7" t="n">
         <v>14176.46561067146</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="P8" s="13" t="n">
         <v>24.72188098218113</v>
       </c>
-      <c r="N8" s="14" t="n">
+      <c r="Q8" s="13" t="n">
         <v>165.580958475509</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="R8" s="7" t="n">
         <v>14135.11069348747</v>
       </c>
-      <c r="P8" s="6" t="inlineStr">
+      <c r="S8" s="6" t="inlineStr">
         <is>
           <t>-4.6％</t>
         </is>
       </c>
-      <c r="Q8" s="9" t="inlineStr"/>
+      <c r="T8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4733,45 +4851,56 @@
       <c r="D9" s="8" t="n">
         <v>9.429319371727749</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="13" t="n">
         <v>29.75</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="13" t="n">
         <v>300.1666666666667</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="7" t="n">
+        <v>76733.02801120449</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>77610.46861748543</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>+1.1％</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="n">
         <v>30.762986909049</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="K9" s="13" t="n">
         <v>290.0740283937029</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="L9" s="7" t="n">
         <v>28650.35796101836</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="M9" s="13" t="n">
         <v>30.67350759866783</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="N9" s="13" t="n">
         <v>289.2302993989568</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="O9" s="7" t="n">
         <v>28567.02358649532</v>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="P9" s="13" t="n">
         <v>30.58402828828665</v>
       </c>
-      <c r="N9" s="14" t="n">
+      <c r="Q9" s="13" t="n">
         <v>288.3865704042107</v>
       </c>
-      <c r="O9" s="7" t="n">
+      <c r="R9" s="7" t="n">
         <v>28483.68921197229</v>
       </c>
-      <c r="P9" s="6" t="inlineStr">
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>-3.9％</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr"/>
+      <c r="T9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4792,45 +4921,60 @@
       <c r="D10" s="8" t="n">
         <v>7.615384615384615</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="13" t="n">
         <v>2.25</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="13" t="n">
         <v>16.5</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="7" t="n">
+        <v>86208.66666666667</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>75093.79041612482</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>-12.9％</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="n">
         <v>2.061249797216939</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="K10" s="13" t="n">
         <v>15.69720999419054</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>1857.444723209863</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="M10" s="13" t="n">
         <v>2.055254306241905</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="N10" s="13" t="n">
         <v>15.65155202445758</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="O10" s="7" t="n">
         <v>1852.042033497211</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="P10" s="13" t="n">
         <v>2.04925881526687</v>
       </c>
-      <c r="N10" s="14" t="n">
+      <c r="Q10" s="13" t="n">
         <v>15.60589405472462</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="R10" s="7" t="n">
         <v>1846.639343784559</v>
       </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="S10" s="6" t="inlineStr">
         <is>
           <t>-5.4％</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>**見込単価が令和7年度実績から10％を超えて離れる。単価も一方向に動いてきたため、3年平均が実績から離れる。件数と単価が逆方向に動くと給付費では打ち消し合う**</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4851,45 +4995,52 @@
       <c r="D11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="14" t="n">
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="14" t="n">
+      <c r="M11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="P11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="T11" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -4914,45 +5065,52 @@
       <c r="D12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="14" t="n">
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="14" t="n">
+      <c r="M12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="6" t="inlineStr">
+      <c r="P12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q12" s="9" t="inlineStr">
+      <c r="T12" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -4975,37 +5133,48 @@
         </is>
       </c>
       <c r="D13" s="10" t="n"/>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="13" t="n">
         <v>198.9166666666667</v>
       </c>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="14" t="n">
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="7" t="n">
+        <v>13114.69710934227</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>12774.25079084056</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>-2.6％</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="n">
         <v>197.6072039103309</v>
       </c>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="7" t="n">
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="7" t="n">
         <v>30291.40776992803</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="M13" s="13" t="n">
         <v>197.0324301933142</v>
       </c>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="7" t="n">
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="7" t="n">
         <v>30203.30012661817</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="P13" s="13" t="n">
         <v>196.4576564762976</v>
       </c>
-      <c r="N13" s="16" t="n"/>
-      <c r="O13" s="7" t="n">
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="7" t="n">
         <v>30115.19248330832</v>
       </c>
-      <c r="P13" s="6" t="inlineStr">
+      <c r="S13" s="6" t="inlineStr">
         <is>
           <t>-1.2％</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr"/>
+      <c r="T13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -5024,86 +5193,108 @@
         </is>
       </c>
       <c r="D14" s="10" t="n"/>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="13" t="n">
         <v>3.75</v>
       </c>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="14" t="n">
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="7" t="n">
+        <v>38278.88888888889</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>36978.74271489034</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>-3.4％</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="n">
         <v>3.430679603262789</v>
       </c>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="7" t="n">
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="7" t="n">
         <v>1522.346620635321</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="M14" s="13" t="n">
         <v>3.420700895865282</v>
       </c>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="7" t="n">
+      <c r="N14" s="14" t="n"/>
+      <c r="O14" s="7" t="n">
         <v>1517.918619993566</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="P14" s="13" t="n">
         <v>3.410722188467776</v>
       </c>
-      <c r="N14" s="16" t="n"/>
-      <c r="O14" s="7" t="n">
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="7" t="n">
         <v>1513.490619351811</v>
       </c>
-      <c r="P14" s="6" t="inlineStr">
+      <c r="S14" s="6" t="inlineStr">
         <is>
           <t>-9.0％</t>
         </is>
       </c>
-      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="T14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>住宅改修</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
       <c r="D15" s="10" t="n"/>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="13" t="n">
         <v>1.833333333333333</v>
       </c>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="14" t="n">
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="7" t="n">
+        <v>82408.77272727272</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>78049.36121597016</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>-5.3％</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="n">
         <v>2.145653241672757</v>
       </c>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="7" t="n">
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="7" t="n">
         <v>2009.602378842412</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="M15" s="13" t="n">
         <v>2.139412249114081</v>
       </c>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="7" t="n">
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="7" t="n">
         <v>2003.757113051712</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="P15" s="13" t="n">
         <v>2.133171256555405</v>
       </c>
-      <c r="N15" s="16" t="n"/>
-      <c r="O15" s="7" t="n">
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="7" t="n">
         <v>1997.911847261013</v>
       </c>
-      <c r="P15" s="13" t="inlineStr">
+      <c r="S15" s="15" t="inlineStr">
         <is>
           <t>+16.4％</t>
         </is>
       </c>
-      <c r="Q15" s="15" t="inlineStr">
+      <c r="T15" s="16" t="inlineStr">
         <is>
           <t>**令和7年度実績から15％を超えて動く。基準期間を令和5〜7年度の3年平均としているため、一方向に動いてきたサービスでは平均に引き戻される。00シートの「趨勢のあるサービスの扱い」を参照**</t>
         </is>
@@ -5126,37 +5317,48 @@
         </is>
       </c>
       <c r="D16" s="10" t="n"/>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="13" t="n">
         <v>3.75</v>
       </c>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="14" t="n">
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="7" t="n">
+        <v>215976.6222222222</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>199991.7284799936</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>-7.4％</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="n">
         <v>3.517437513922497</v>
       </c>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="7" t="n">
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="7" t="n">
         <v>8441.500898756782</v>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="M16" s="13" t="n">
         <v>3.507206456581244</v>
       </c>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="7" t="n">
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="7" t="n">
         <v>8416.947376654523</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="P16" s="13" t="n">
         <v>3.496975399239993</v>
       </c>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="7" t="n">
+      <c r="Q16" s="14" t="n"/>
+      <c r="R16" s="7" t="n">
         <v>8392.393854552263</v>
       </c>
-      <c r="P16" s="6" t="inlineStr">
+      <c r="S16" s="6" t="inlineStr">
         <is>
           <t>-6.7％</t>
         </is>
       </c>
-      <c r="Q16" s="9" t="inlineStr"/>
+      <c r="T16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -5166,7 +5368,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援</t>
+          <t>居宅介護支援</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5175,37 +5377,48 @@
         </is>
       </c>
       <c r="D17" s="10" t="n"/>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="13" t="n">
         <v>253</v>
       </c>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="14" t="n">
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="7" t="n">
+        <v>15836.85540184453</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>15870.6116614193</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>+0.2％</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="n">
         <v>259.9002413773233</v>
       </c>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="7" t="n">
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="7" t="n">
         <v>49497.30961930367</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="M17" s="13" t="n">
         <v>259.1442779061851</v>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="7" t="n">
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="7" t="n">
         <v>49353.33838713582</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="P17" s="13" t="n">
         <v>258.3883144350469</v>
       </c>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="7" t="n">
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="7" t="n">
         <v>49209.36715496798</v>
       </c>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="S17" s="6" t="inlineStr">
         <is>
           <t>+2.1％</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr"/>
+      <c r="T17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -5224,37 +5437,44 @@
         </is>
       </c>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="16" t="n"/>
+      <c r="E18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="n"/>
       <c r="L18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="16" t="n"/>
+      <c r="M18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="14" t="n"/>
       <c r="O18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="6" t="inlineStr">
+      <c r="P18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q18" s="9" t="inlineStr"/>
+      <c r="T18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5273,37 +5493,44 @@
         </is>
       </c>
       <c r="D19" s="10" t="n"/>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="16" t="n"/>
+      <c r="E19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14" t="n"/>
       <c r="L19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="16" t="n"/>
+      <c r="M19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="14" t="n"/>
       <c r="O19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="6" t="inlineStr">
+      <c r="P19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="14" t="n"/>
+      <c r="R19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q19" s="9" t="inlineStr"/>
+      <c r="T19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -5324,45 +5551,52 @@
       <c r="D20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="14" t="n">
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="14" t="n">
+      <c r="M20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="6" t="inlineStr">
+      <c r="P20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q20" s="9" t="inlineStr">
+      <c r="T20" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -5387,45 +5621,56 @@
       <c r="D21" s="8" t="n">
         <v>9.452173913043477</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="13" t="n">
         <v>9.583333333333334</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="13" t="n">
         <v>90.58333333333333</v>
       </c>
-      <c r="G21" s="14" t="n">
+      <c r="G21" s="7" t="n">
+        <v>106415.6869565217</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>112682.6952285764</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>+5.9％</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="n">
         <v>8.411820861755876</v>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="K21" s="13" t="n">
         <v>79.50999371068379</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="L21" s="7" t="n">
         <v>11374.39975779142</v>
       </c>
-      <c r="J21" s="14" t="n">
+      <c r="M21" s="13" t="n">
         <v>8.387353669022437</v>
       </c>
-      <c r="K21" s="14" t="n">
+      <c r="N21" s="13" t="n">
         <v>79.27872554980338</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="O21" s="7" t="n">
         <v>11341.31540712885</v>
       </c>
-      <c r="M21" s="14" t="n">
+      <c r="P21" s="13" t="n">
         <v>8.362886476289001</v>
       </c>
-      <c r="N21" s="14" t="n">
+      <c r="Q21" s="13" t="n">
         <v>79.04745738892298</v>
       </c>
-      <c r="O21" s="7" t="n">
+      <c r="R21" s="7" t="n">
         <v>11308.23105646628</v>
       </c>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="S21" s="6" t="inlineStr">
         <is>
           <t>-12.7％</t>
         </is>
       </c>
-      <c r="Q21" s="9" t="inlineStr"/>
+      <c r="T21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5444,37 +5689,48 @@
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="13" t="n">
         <v>22.5</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="14" t="n">
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="7" t="n">
+        <v>183625.2666666667</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>174505.617755753</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>-5.0％</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="n">
         <v>24.74089762862516</v>
       </c>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="7" t="n">
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="7" t="n">
         <v>51809.10749418093</v>
       </c>
-      <c r="J22" s="14" t="n">
+      <c r="M22" s="13" t="n">
         <v>24.66893457560414</v>
       </c>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="7" t="n">
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="7" t="n">
         <v>51658.41200990466</v>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="P22" s="13" t="n">
         <v>24.59697152258313</v>
       </c>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="7" t="n">
+      <c r="Q22" s="14" t="n"/>
+      <c r="R22" s="7" t="n">
         <v>51507.7165256284</v>
       </c>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="S22" s="6" t="inlineStr">
         <is>
           <t>+9.3％</t>
         </is>
       </c>
-      <c r="Q22" s="9" t="inlineStr"/>
+      <c r="T22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5493,37 +5749,48 @@
         </is>
       </c>
       <c r="D23" s="10" t="n"/>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="13" t="n">
         <v>44.75</v>
       </c>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="14" t="n">
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="7" t="n">
+        <v>250242.1508379888</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>254789.1248438966</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>+1.8％</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="n">
         <v>48.25028634922224</v>
       </c>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="7" t="n">
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="7" t="n">
         <v>147523.778788629</v>
       </c>
-      <c r="J23" s="14" t="n">
+      <c r="M23" s="13" t="n">
         <v>48.10994229352351</v>
       </c>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="7" t="n">
+      <c r="N23" s="14" t="n"/>
+      <c r="O23" s="7" t="n">
         <v>147094.6811190867</v>
       </c>
-      <c r="M23" s="14" t="n">
+      <c r="P23" s="13" t="n">
         <v>47.96959823782478</v>
       </c>
-      <c r="N23" s="16" t="n"/>
-      <c r="O23" s="7" t="n">
+      <c r="Q23" s="14" t="n"/>
+      <c r="R23" s="7" t="n">
         <v>146665.5834495444</v>
       </c>
-      <c r="P23" s="6" t="inlineStr">
+      <c r="S23" s="6" t="inlineStr">
         <is>
           <t>+7.2％</t>
         </is>
       </c>
-      <c r="Q23" s="9" t="inlineStr"/>
+      <c r="T23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5542,37 +5809,44 @@
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
-      <c r="E24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="16" t="n"/>
+      <c r="E24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="14" t="n"/>
       <c r="L24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="16" t="n"/>
+      <c r="M24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="14" t="n"/>
       <c r="O24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="6" t="inlineStr">
+      <c r="P24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="14" t="n"/>
+      <c r="R24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q24" s="9" t="inlineStr"/>
+      <c r="T24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5591,37 +5865,48 @@
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="13" t="n">
         <v>41.33333333333334</v>
       </c>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="14" t="n">
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="7" t="n">
+        <v>254737.1310483871</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>249304.1190012729</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>-2.1％</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="n">
         <v>43.42209804447699</v>
       </c>
-      <c r="H25" s="16" t="n"/>
-      <c r="I25" s="7" t="n">
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="7" t="n">
         <v>129903.6947779828</v>
       </c>
-      <c r="J25" s="14" t="n">
+      <c r="M25" s="13" t="n">
         <v>43.29579758477811</v>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="7" t="n">
+      <c r="N25" s="14" t="n"/>
+      <c r="O25" s="7" t="n">
         <v>129525.8480799665</v>
       </c>
-      <c r="M25" s="14" t="n">
+      <c r="P25" s="13" t="n">
         <v>43.16949712507921</v>
       </c>
-      <c r="N25" s="16" t="n"/>
-      <c r="O25" s="7" t="n">
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="7" t="n">
         <v>129148.0013819503</v>
       </c>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="S25" s="6" t="inlineStr">
         <is>
           <t>+4.4％</t>
         </is>
       </c>
-      <c r="Q25" s="9" t="inlineStr"/>
+      <c r="T25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5640,37 +5925,44 @@
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
-      <c r="E26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="16" t="n"/>
+      <c r="E26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="14" t="n"/>
       <c r="L26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="16" t="n"/>
+      <c r="M26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="14" t="n"/>
       <c r="O26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P26" s="6" t="inlineStr">
+      <c r="P26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="14" t="n"/>
+      <c r="R26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q26" s="9" t="inlineStr"/>
+      <c r="T26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5689,37 +5981,48 @@
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="13" t="n">
         <v>68.91666666666667</v>
       </c>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="14" t="n">
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="7" t="n">
+        <v>247702.1039903265</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>250649.2353616817</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>+1.2％</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="n">
         <v>67.96849214798212</v>
       </c>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="7" t="n">
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="7" t="n">
         <v>204435.0070269382</v>
       </c>
-      <c r="J27" s="14" t="n">
+      <c r="M27" s="13" t="n">
         <v>67.77079438140858</v>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="7" t="n">
+      <c r="N27" s="14" t="n"/>
+      <c r="O27" s="7" t="n">
         <v>203840.3734986458</v>
       </c>
-      <c r="M27" s="14" t="n">
+      <c r="P27" s="13" t="n">
         <v>67.57309661483505</v>
       </c>
-      <c r="N27" s="16" t="n"/>
-      <c r="O27" s="7" t="n">
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="7" t="n">
         <v>203245.7399703533</v>
       </c>
-      <c r="P27" s="6" t="inlineStr">
+      <c r="S27" s="6" t="inlineStr">
         <is>
           <t>-1.9％</t>
         </is>
       </c>
-      <c r="Q27" s="9" t="inlineStr"/>
+      <c r="T27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5738,37 +6041,48 @@
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="13" t="n">
         <v>28.58333333333333</v>
       </c>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="14" t="n">
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="7" t="n">
+        <v>269746.5801749271</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>273430.6329498911</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>+1.4％</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="n">
         <v>29.58179131592092</v>
       </c>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="7" t="n">
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="7" t="n">
         <v>97062.81507964619</v>
       </c>
-      <c r="J28" s="14" t="n">
+      <c r="M28" s="13" t="n">
         <v>29.49574771116257</v>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="7" t="n">
+      <c r="N28" s="14" t="n"/>
+      <c r="O28" s="7" t="n">
         <v>96780.49159192179</v>
       </c>
-      <c r="M28" s="14" t="n">
+      <c r="P28" s="13" t="n">
         <v>29.40970410640422</v>
       </c>
-      <c r="N28" s="16" t="n"/>
-      <c r="O28" s="7" t="n">
+      <c r="Q28" s="14" t="n"/>
+      <c r="R28" s="7" t="n">
         <v>96498.16810419739</v>
       </c>
-      <c r="P28" s="6" t="inlineStr">
+      <c r="S28" s="6" t="inlineStr">
         <is>
           <t>+2.9％</t>
         </is>
       </c>
-      <c r="Q28" s="9" t="inlineStr"/>
+      <c r="T28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5787,37 +6101,44 @@
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
-      <c r="E29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="16" t="n"/>
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="14" t="n"/>
       <c r="L29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="16" t="n"/>
+      <c r="M29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="14" t="n"/>
       <c r="O29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P29" s="6" t="inlineStr">
+      <c r="P29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="14" t="n"/>
+      <c r="R29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q29" s="9" t="inlineStr"/>
+      <c r="T29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -5836,37 +6157,48 @@
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="13" t="n">
         <v>1.166666666666667</v>
       </c>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="14" t="n">
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="7" t="n">
+        <v>307830.8571428572</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>307830.8571428572</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>+0.0％</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="n">
         <v>1.164972407783909</v>
       </c>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="7" t="n">
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="7" t="n">
         <v>4303.373458030787</v>
       </c>
-      <c r="J30" s="14" t="n">
+      <c r="M30" s="13" t="n">
         <v>1.161583890018395</v>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="7" t="n">
+      <c r="N30" s="14" t="n"/>
+      <c r="O30" s="7" t="n">
         <v>4290.856374092362</v>
       </c>
-      <c r="M30" s="14" t="n">
+      <c r="P30" s="13" t="n">
         <v>1.15819537225288</v>
       </c>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="7" t="n">
+      <c r="Q30" s="14" t="n"/>
+      <c r="R30" s="7" t="n">
         <v>4278.339290153936</v>
       </c>
-      <c r="P30" s="6" t="inlineStr">
+      <c r="S30" s="6" t="inlineStr">
         <is>
           <t>-0.7％</t>
         </is>
       </c>
-      <c r="Q30" s="9" t="inlineStr"/>
+      <c r="T30" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -5893,6 +6225,13 @@
       <c r="A35" s="12" t="inlineStr">
         <is>
           <t>※ 給付費は年報から組んだ試算による。報酬改定率は0.0％で置いている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>**※ 「見込単価」は見込給付費÷見込件数。件数と給付費をそれぞれ令和5〜7年度の平均で置いているため、両者の比である単価は令和7年度実績と一致しない。**10％を超えて離れるのは訪問介護（▲13.8％）と短期入所療養介護（老健）（▲12.9％）の2件。</t>
         </is>
       </c>
     </row>
@@ -5907,18 +6246,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -5926,7 +6265,10 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5962,55 +6304,70 @@
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
+          <t>R7 単価(円/件)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>見込単価(円/件)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>単価の乖離</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
           <t>9年度 人/月</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>9年度 量/月</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>9年度 給付費(千円)</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>10年度 人/月</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>10年度 量/月</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>10年度 給付費(千円)</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>11年度 人/月</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>11年度 量/月</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>11年度 給付費(千円)</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>R7→R11</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -6024,7 +6381,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>訪問入浴介護</t>
+          <t>介護予防訪問入浴介護</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -6035,62 +6392,69 @@
       <c r="D2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="14" t="n">
+      <c r="E2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="14" t="n">
+      <c r="M2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="6" t="inlineStr">
+      <c r="P2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q2" s="9" t="inlineStr">
+      <c r="T2" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>訪問看護</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>介護予防訪問看護</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>回</t>
         </is>
@@ -6098,45 +6462,56 @@
       <c r="D3" s="8" t="n">
         <v>3.89873417721519</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="13" t="n">
         <v>7.333333333333333</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="13" t="n">
         <v>25.66666666666667</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="G3" s="7" t="n">
+        <v>25157.03409090909</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>27670.64599414647</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>+10.0％</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="n">
         <v>5.557699607338822</v>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="K3" s="13" t="n">
         <v>21.66799340582731</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="L3" s="7" t="n">
         <v>1845.421660517753</v>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="M3" s="13" t="n">
         <v>5.541534105281408</v>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="N3" s="13" t="n">
         <v>21.60496841046422</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="O3" s="7" t="n">
         <v>1840.053941900773</v>
       </c>
-      <c r="M3" s="14" t="n">
+      <c r="P3" s="13" t="n">
         <v>5.525368603223995</v>
       </c>
-      <c r="N3" s="14" t="n">
+      <c r="Q3" s="13" t="n">
         <v>21.54194341510114</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="R3" s="7" t="n">
         <v>1834.686223283793</v>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="S3" s="15" t="inlineStr">
         <is>
           <t>-16.1％</t>
         </is>
       </c>
-      <c r="Q3" s="15" t="inlineStr">
+      <c r="T3" s="16" t="inlineStr">
         <is>
           <t>**令和7年度実績から15％を超えて動く。基準期間を令和5〜7年度の3年平均としているため、一方向に動いてきたサービスでは平均に引き戻される。00シートの「趨勢のあるサービスの扱い」を参照**</t>
         </is>
@@ -6150,7 +6525,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>訪問リハビリテーション</t>
+          <t>介護予防訪問リハビリテーション</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -6161,45 +6536,52 @@
       <c r="D4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="14" t="n">
+      <c r="E4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="14" t="n">
+      <c r="M4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -6213,7 +6595,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>居宅療養管理指導</t>
+          <t>介護予防居宅療養管理指導</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -6222,37 +6604,48 @@
         </is>
       </c>
       <c r="D5" s="10" t="n"/>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <v>2.083333333333333</v>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="14" t="n">
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="7" t="n">
+        <v>5294.88</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>5354.206863798503</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>+1.1％</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="n">
         <v>2.005774920655801</v>
       </c>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="7" t="n">
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="7" t="n">
         <v>128.8720061689222</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="M5" s="13" t="n">
         <v>1.9999407876696</v>
       </c>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="7" t="n">
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="7" t="n">
         <v>128.4971603103739</v>
       </c>
-      <c r="M5" s="14" t="n">
+      <c r="P5" s="13" t="n">
         <v>1.994106654683399</v>
       </c>
-      <c r="N5" s="16" t="n"/>
-      <c r="O5" s="7" t="n">
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="7" t="n">
         <v>128.1223144518255</v>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="S5" s="6" t="inlineStr">
         <is>
           <t>-4.3％</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr"/>
+      <c r="T5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6262,7 +6655,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>通所リハビリテーション</t>
+          <t>介護予防通所リハビリテーション</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -6273,58 +6666,69 @@
       <c r="D6" s="8" t="n">
         <v>6.316417910447761</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <v>27.41666666666667</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="13" t="n">
         <v>176.3333333333333</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="7" t="n">
+        <v>35529.34346504559</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>37630.6414898314</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>+5.9％</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="n">
         <v>24.38155764664053</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="K6" s="13" t="n">
         <v>154.0041074038548</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="L6" s="7" t="n">
         <v>11009.92385717264</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="M6" s="13" t="n">
         <v>24.31063979426519</v>
       </c>
-      <c r="K6" s="14" t="n">
+      <c r="N6" s="13" t="n">
         <v>153.5561606109407</v>
       </c>
-      <c r="L6" s="7" t="n">
+      <c r="O6" s="7" t="n">
         <v>10977.89964583706</v>
       </c>
-      <c r="M6" s="14" t="n">
+      <c r="P6" s="13" t="n">
         <v>24.23972194188985</v>
       </c>
-      <c r="N6" s="14" t="n">
+      <c r="Q6" s="13" t="n">
         <v>153.1082138180267</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="R6" s="7" t="n">
         <v>10945.87543450148</v>
       </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>-13.2％</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="inlineStr"/>
+      <c r="T6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>短期入所生活介護</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>介護予防短期入所生活介護</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>日</t>
         </is>
@@ -6332,47 +6736,58 @@
       <c r="D7" s="8" t="n">
         <v>5.2</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13" t="n">
         <v>0.75</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="13" t="n">
         <v>4.333333333333333</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="7" t="n">
+        <v>32551</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>27949.48732952393</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>-14.1％</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="n">
         <v>0.4410197100561855</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="K7" s="13" t="n">
         <v>2.293302492292165</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="L7" s="7" t="n">
         <v>147.9152975794281</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="M7" s="13" t="n">
         <v>0.4397369302130902</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="N7" s="13" t="n">
         <v>2.286632037108069</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="O7" s="7" t="n">
         <v>147.4850611117741</v>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="P7" s="13" t="n">
         <v>0.4384541503699949</v>
       </c>
-      <c r="N7" s="14" t="n">
+      <c r="Q7" s="13" t="n">
         <v>2.279961581923974</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="R7" s="7" t="n">
         <v>147.0548246441202</v>
       </c>
-      <c r="P7" s="13" t="inlineStr">
+      <c r="S7" s="6" t="inlineStr">
         <is>
           <t>-47.4％</t>
         </is>
       </c>
-      <c r="Q7" s="15" t="inlineStr">
-        <is>
-          <t>**令和7年度実績から15％を超えて動く。基準期間を令和5〜7年度の3年平均としているため、一方向に動いてきたサービスでは平均に引き戻される。00シートの「趨勢のあるサービスの扱い」を参照**</t>
+      <c r="T7" s="9" t="inlineStr">
+        <is>
+          <t>**見込単価が令和7年度実績から10％を超えて離れる。単価も一方向に動いてきたため、3年平均が実績から離れる。件数と単価が逆方向に動くと給付費では打ち消し合う**</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6799,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（介護老人保健施設）</t>
+          <t>介護予防短期入所療養介護（介護老人保健施設）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -6395,45 +6810,60 @@
       <c r="D8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="13" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="13" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="7" t="n">
+        <v>50004</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>58459.79788378457</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>+16.9％</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="n">
         <v>0.0824182284323013</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="K8" s="13" t="n">
         <v>0.4120911421615066</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="L8" s="7" t="n">
         <v>57.81783571310305</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="M8" s="13" t="n">
         <v>0.08217850118264365</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="N8" s="13" t="n">
         <v>0.4108925059132183</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="O8" s="7" t="n">
         <v>57.64966283435638</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="P8" s="13" t="n">
         <v>0.081938773932986</v>
       </c>
-      <c r="N8" s="14" t="n">
+      <c r="Q8" s="13" t="n">
         <v>0.40969386966493</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="R8" s="7" t="n">
         <v>57.48148995560972</v>
       </c>
-      <c r="P8" s="6" t="inlineStr">
+      <c r="S8" s="6" t="inlineStr">
         <is>
           <t>-1.7％</t>
         </is>
       </c>
-      <c r="Q8" s="9" t="inlineStr"/>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>**見込単価が令和7年度実績から10％を超えて離れる。単価も一方向に動いてきたため、3年平均が実績から離れる。件数と単価が逆方向に動くと給付費では打ち消し合う**</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6443,7 +6873,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（病院等）</t>
+          <t>介護予防短期入所療養介護（病院等）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -6454,45 +6884,52 @@
       <c r="D9" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="14" t="n">
+      <c r="E9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="14" t="n">
+      <c r="M9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="6" t="inlineStr">
+      <c r="P9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="T9" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -6506,7 +6943,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（介護医療院）</t>
+          <t>介護予防短期入所療養介護（介護医療院）</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6517,45 +6954,52 @@
       <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="14" t="n">
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="14" t="n">
+      <c r="M10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="P10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="T10" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -6569,7 +7013,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>福祉用具貸与</t>
+          <t>介護予防福祉用具貸与</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -6578,86 +7022,108 @@
         </is>
       </c>
       <c r="D11" s="10" t="n"/>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="13" t="n">
         <v>57.33333333333334</v>
       </c>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="14" t="n">
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="7" t="n">
+        <v>8721.492732558139</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>8305.223344467251</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>-4.8％</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="n">
         <v>52.21991636898127</v>
       </c>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="7" t="n">
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="7" t="n">
         <v>5204.376821685491</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="M11" s="13" t="n">
         <v>52.06802597814654</v>
       </c>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="7" t="n">
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="7" t="n">
         <v>5189.23901824836</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="P11" s="13" t="n">
         <v>51.91613558731181</v>
       </c>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="7" t="n">
+      <c r="Q11" s="14" t="n"/>
+      <c r="R11" s="7" t="n">
         <v>5174.10121481123</v>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>-9.4％</t>
         </is>
       </c>
-      <c r="Q11" s="9" t="inlineStr"/>
+      <c r="T11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>特定福祉用具販売</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>特定介護予防福祉用具販売</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
       <c r="D12" s="10" t="n"/>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="13" t="n">
         <v>1.416666666666667</v>
       </c>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="14" t="n">
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="7" t="n">
+        <v>28474.11764705883</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>28229.15434422077</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>-0.9％</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="n">
         <v>1.199431787520105</v>
       </c>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="7" t="n">
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="7" t="n">
         <v>406.3073406632359</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="M12" s="13" t="n">
         <v>1.195943038865305</v>
       </c>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="7" t="n">
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="7" t="n">
         <v>405.1255275723015</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="P12" s="13" t="n">
         <v>1.192454290210506</v>
       </c>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="7" t="n">
+      <c r="Q12" s="14" t="n"/>
+      <c r="R12" s="7" t="n">
         <v>403.9437144813671</v>
       </c>
-      <c r="P12" s="13" t="inlineStr">
+      <c r="S12" s="15" t="inlineStr">
         <is>
           <t>-15.8％</t>
         </is>
       </c>
-      <c r="Q12" s="15" t="inlineStr">
+      <c r="T12" s="16" t="inlineStr">
         <is>
           <t>**令和7年度実績から15％を超えて動く。基準期間を令和5〜7年度の3年平均としているため、一方向に動いてきたサービスでは平均に引き戻される。00シートの「趨勢のあるサービスの扱い」を参照**</t>
         </is>
@@ -6671,7 +7137,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>住宅改修</t>
+          <t>介護予防住宅改修</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -6680,37 +7146,52 @@
         </is>
       </c>
       <c r="D13" s="10" t="n"/>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="14" t="n">
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="7" t="n">
+        <v>79704.45454545454</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>97687.71974706066</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>+22.6％</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="n">
         <v>0.9908054356087804</v>
       </c>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="7" t="n">
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="7" t="n">
         <v>1161.474284611379</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="M13" s="13" t="n">
         <v>0.9879235117123034</v>
       </c>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="7" t="n">
+      <c r="N13" s="14" t="n"/>
+      <c r="O13" s="7" t="n">
         <v>1158.095941724202</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="P13" s="13" t="n">
         <v>0.9850415878158264</v>
       </c>
-      <c r="N13" s="16" t="n"/>
-      <c r="O13" s="7" t="n">
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="7" t="n">
         <v>1154.717598837025</v>
       </c>
-      <c r="P13" s="6" t="inlineStr">
+      <c r="S13" s="6" t="inlineStr">
         <is>
           <t>+7.5％</t>
         </is>
       </c>
-      <c r="Q13" s="9" t="inlineStr"/>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>**見込単価が令和7年度実績から10％を超えて離れる。単価も一方向に動いてきたため、3年平均が実績から離れる。件数と単価が逆方向に動くと給付費では打ち消し合う**</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -6720,7 +7201,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護</t>
+          <t>介護予防特定施設入居者生活介護</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -6729,37 +7210,44 @@
         </is>
       </c>
       <c r="D14" s="10" t="n"/>
-      <c r="E14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="16" t="n"/>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14" t="n"/>
       <c r="L14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="16" t="n"/>
+      <c r="M14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="14" t="n"/>
       <c r="O14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="6" t="inlineStr">
+      <c r="P14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="14" t="n"/>
+      <c r="R14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q14" s="9" t="inlineStr"/>
+      <c r="T14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -6769,7 +7257,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援</t>
+          <t>介護予防支援</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -6778,37 +7266,48 @@
         </is>
       </c>
       <c r="D15" s="10" t="n"/>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="13" t="n">
         <v>76.58333333333333</v>
       </c>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="14" t="n">
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="7" t="n">
+        <v>4511.403699673559</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>4510.739575690291</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>-0.0％</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="n">
         <v>69.48140145691158</v>
       </c>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="7" t="n">
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="7" t="n">
         <v>3760.950087913393</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="M15" s="13" t="n">
         <v>69.27930313970126</v>
       </c>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="7" t="n">
+      <c r="N15" s="14" t="n"/>
+      <c r="O15" s="7" t="n">
         <v>3750.010733381941</v>
       </c>
-      <c r="M15" s="14" t="n">
+      <c r="P15" s="13" t="n">
         <v>69.07720482249093</v>
       </c>
-      <c r="N15" s="16" t="n"/>
-      <c r="O15" s="7" t="n">
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="7" t="n">
         <v>3739.071378850489</v>
       </c>
-      <c r="P15" s="6" t="inlineStr">
+      <c r="S15" s="6" t="inlineStr">
         <is>
           <t>-9.8％</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr"/>
+      <c r="T15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -6818,7 +7317,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護</t>
+          <t>介護予防認知症対応型通所介護</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -6829,45 +7328,52 @@
       <c r="D16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="14" t="n">
+      <c r="E16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="14" t="n">
+      <c r="M16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="6" t="inlineStr">
+      <c r="P16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="Q16" s="9" t="inlineStr">
+      <c r="T16" s="9" t="inlineStr">
         <is>
           <t>**月報に実績がないため量は出せない。人数のみ**</t>
         </is>
@@ -6881,7 +7387,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護</t>
+          <t>介護予防小規模多機能型居宅介護</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -6890,86 +7396,108 @@
         </is>
       </c>
       <c r="D17" s="10" t="n"/>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="13" t="n">
         <v>7.666666666666667</v>
       </c>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="14" t="n">
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="7" t="n">
+        <v>79218.68478260869</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>78518.68233595132</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>-0.9％</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="n">
         <v>6.707584373344008</v>
       </c>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="7" t="n">
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="7" t="n">
         <v>6320.048239826271</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="M17" s="13" t="n">
         <v>6.688074238459354</v>
       </c>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="7" t="n">
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="7" t="n">
         <v>6301.665318826195</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="P17" s="13" t="n">
         <v>6.6685641035747</v>
       </c>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="7" t="n">
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="7" t="n">
         <v>6283.282397826119</v>
       </c>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="S17" s="6" t="inlineStr">
         <is>
           <t>-13.0％</t>
         </is>
       </c>
-      <c r="Q17" s="9" t="inlineStr"/>
+      <c r="T17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>地域密着型</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>介護予防認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>人</t>
         </is>
       </c>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="13" t="n">
         <v>1.166666666666667</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="14" t="n">
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="7" t="n">
+        <v>238812.4285714286</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>232517.0685324384</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>-2.6％</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="n">
         <v>2.247471001086859</v>
       </c>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="7" t="n">
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="7" t="n">
         <v>6270.904425412573</v>
       </c>
-      <c r="J18" s="14" t="n">
+      <c r="M18" s="13" t="n">
         <v>2.240933854486839</v>
       </c>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="7" t="n">
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="7" t="n">
         <v>6252.664447444531</v>
       </c>
-      <c r="M18" s="14" t="n">
+      <c r="P18" s="13" t="n">
         <v>2.234396707886819</v>
       </c>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="7" t="n">
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="7" t="n">
         <v>6234.42446947649</v>
       </c>
-      <c r="P18" s="13" t="inlineStr">
+      <c r="S18" s="15" t="inlineStr">
         <is>
           <t>+91.5％</t>
         </is>
       </c>
-      <c r="Q18" s="15" t="inlineStr">
+      <c r="T18" s="16" t="inlineStr">
         <is>
           <t>**令和7年度実績から15％を超えて動く。基準期間を令和5〜7年度の3年平均としているため、一方向に動いてきたサービスでは平均に引き戻される。00シートの「趨勢のあるサービスの扱い」を参照**</t>
         </is>
@@ -7000,6 +7528,13 @@
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>※ 給付費は年報から組んだ試算による。報酬改定率は0.0％で置いている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>**※ 「見込単価」は見込給付費÷見込件数。件数と給付費をそれぞれ令和5〜7年度の平均で置いているため、両者の比である単価は令和7年度実績と一致しない。**10％を超えて離れるのは訪問介護（▲13.8％）と短期入所療養介護（老健）（▲12.9％）の2件。</t>
         </is>
       </c>
     </row>
@@ -7014,11 +7549,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -7121,16 +7656,16 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="13" t="n">
         <v>52.3</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="13" t="n">
         <v>66.7</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="13" t="n">
         <v>66.5</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="13" t="n">
         <v>66.3</v>
       </c>
       <c r="H4" s="9" t="inlineStr"/>
@@ -7173,16 +7708,16 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <v>5.7</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <v>6.5</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="13" t="n">
         <v>6.5</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="13" t="n">
         <v>6.5</v>
       </c>
       <c r="H6" s="9" t="inlineStr"/>
@@ -7225,16 +7760,16 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="13" t="n">
         <v>43.2</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="13" t="n">
         <v>39.7</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="13" t="n">
         <v>39.6</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="13" t="n">
         <v>39.5</v>
       </c>
       <c r="H8" s="9" t="inlineStr"/>
@@ -7252,54 +7787,46 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>回/月</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>居宅療養管理指導</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>17</v>
+      <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H10" s="9" t="inlineStr"/>
     </row>
@@ -7311,239 +7838,235 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>通所介護</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>日/月</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D12" s="7" t="n">
         <v>1507</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E12" s="7" t="n">
         <v>1562</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F12" s="7" t="n">
         <v>1557</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G12" s="7" t="n">
         <v>1553</v>
       </c>
-      <c r="H11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="6" t="inlineStr"/>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D13" s="13" t="n">
         <v>171.1</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E13" s="13" t="n">
         <v>177.5</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F13" s="13" t="n">
         <v>177</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G13" s="13" t="n">
         <v>176.5</v>
       </c>
-      <c r="H12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>通所リハビリテーション</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>日/月</t>
         </is>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D14" s="7" t="n">
         <v>174</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E14" s="7" t="n">
         <v>167</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F14" s="7" t="n">
         <v>166</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>166</v>
       </c>
-      <c r="H13" s="9" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D15" s="13" t="n">
         <v>25.9</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E15" s="13" t="n">
         <v>24.9</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F15" s="13" t="n">
         <v>24.8</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G15" s="13" t="n">
         <v>24.7</v>
       </c>
-      <c r="H14" s="9" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>短期入所生活介護</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>日/月</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D16" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E16" s="7" t="n">
         <v>290</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F16" s="7" t="n">
         <v>289</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G16" s="7" t="n">
         <v>288</v>
       </c>
-      <c r="H15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D17" s="13" t="n">
         <v>29.8</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E17" s="13" t="n">
         <v>30.8</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F17" s="13" t="n">
         <v>30.7</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G17" s="13" t="n">
         <v>30.6</v>
       </c>
-      <c r="H16" s="9" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>居宅</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>短期入所療養介護（介護老人保健施設）</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>日/月</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D18" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E18" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F18" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G18" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="H17" s="9" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="6" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D19" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E19" s="13" t="n">
         <v>2.1</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F19" s="13" t="n">
         <v>2.1</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G19" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>短期入所療養介護（病院等）</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
+      <c r="H19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -7553,59 +8076,51 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（介護医療院）</t>
+          <t>短期入所療養介護（病院等）</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>福祉用具貸与</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>198.9</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>197.6</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>197</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>196.5</v>
+      <c r="D21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H21" s="9" t="inlineStr"/>
     </row>
@@ -7617,55 +8132,51 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>特定福祉用具販売</t>
+          <t>短期入所療養介護（介護医療院）</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D22" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>住宅改修</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>2.1</v>
+      <c r="D23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H23" s="9" t="inlineStr"/>
     </row>
@@ -7677,7 +8188,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護</t>
+          <t>福祉用具貸与</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -7685,17 +8196,17 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D24" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>3.5</v>
+      <c r="D24" s="13" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>197.6</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>197</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>196.5</v>
       </c>
       <c r="H24" s="9" t="inlineStr"/>
     </row>
@@ -7707,7 +8218,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援</t>
+          <t>特定福祉用具販売</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -7715,29 +8226,29 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
-        <v>253</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>259.9</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>259.1</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>258.4</v>
+      <c r="D25" s="13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>3.4</v>
       </c>
       <c r="H25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>地域密着型</t>
+          <t>居宅</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護</t>
+          <t>住宅改修</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7745,29 +8256,29 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>0</v>
+      <c r="D26" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>2.1</v>
       </c>
       <c r="H26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>地域密着型</t>
+          <t>居宅</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護</t>
+          <t>特定施設入居者生活介護</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7775,29 +8286,29 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>0</v>
+      <c r="D27" s="13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>3.5</v>
       </c>
       <c r="H27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>地域密着型</t>
+          <t>居宅</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>地域密着型通所介護</t>
+          <t>居宅介護支援</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7805,23 +8316,19 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
+      <c r="D28" s="13" t="n">
+        <v>253</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>259.9</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7831,47 +8338,55 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護</t>
+          <t>定期巡回・随時対応型訪問介護看護</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>日/月</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>79</v>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr"/>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護</t>
+        </is>
+      </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>8.4</v>
+      <c r="D30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H30" s="9" t="inlineStr"/>
     </row>
@@ -7883,55 +8398,51 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護</t>
+          <t>地域密着型通所介護</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="H31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>48</v>
+      <c r="D32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H32" s="9" t="inlineStr"/>
     </row>
@@ -7943,55 +8454,47 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>地域密着型特定施設入居者生活介護</t>
+          <t>認知症対応型通所介護</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="H33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="9" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型介護老人福祉施設入所者生活介護</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>43.2</v>
+      <c r="D34" s="13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>8.4</v>
       </c>
       <c r="H34" s="9" t="inlineStr"/>
     </row>
@@ -8003,7 +8506,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>看護小規模多機能型居宅介護</t>
+          <t>小規模多機能型居宅介護</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -8011,29 +8514,29 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>0</v>
+      <c r="D35" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>24.6</v>
       </c>
       <c r="H35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>施設</t>
+          <t>地域密着型</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>介護老人福祉施設</t>
+          <t>認知症対応型共同生活介護</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -8041,29 +8544,29 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D36" s="14" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>68</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="G36" s="14" t="n">
-        <v>67.59999999999999</v>
+      <c r="D36" s="13" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>48</v>
       </c>
       <c r="H36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>施設</t>
+          <t>地域密着型</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設</t>
+          <t>地域密着型特定施設入居者生活介護</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -8071,29 +8574,29 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D37" s="14" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>29.4</v>
+      <c r="D37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>施設</t>
+          <t>地域密着型</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>介護療養型医療施設</t>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -8101,73 +8604,89 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="14" t="n">
-        <v>0</v>
+      <c r="D38" s="13" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>43.2</v>
       </c>
       <c r="H38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
+          <t>地域密着型</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>看護小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
           <t>施設</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>介護医療院</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D39" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>■ 予防給付（要支援1・2）</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="18" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="19" t="n"/>
+      <c r="D40" s="13" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>居宅</t>
+          <t>施設</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>訪問入浴介護</t>
+          <t>介護老人保健施設</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -8175,139 +8694,123 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
+      <c r="D41" s="13" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>居宅</t>
+          <t>施設</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>訪問看護</t>
+          <t>介護療養型医療施設</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>回/月</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>22</v>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr"/>
-      <c r="B43" s="6" t="inlineStr"/>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>施設</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D43" s="14" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G43" s="14" t="n">
-        <v>5.5</v>
+      <c r="D43" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>1.2</v>
       </c>
       <c r="H43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>訪問リハビリテーション</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>介護給付　利用者数の合計</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr"/>
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
+      <c r="D44" s="21" t="n">
+        <v>1024.6</v>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>1055.3</v>
+      </c>
+      <c r="F44" s="21" t="n">
+        <v>1052.2</v>
+      </c>
+      <c r="G44" s="21" t="n">
+        <v>1049.2</v>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>延べ利用者数。重複を含む</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>居宅療養管理指導</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="9" t="inlineStr"/>
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>■ 予防給付（要支援1・2）</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="19" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -8317,27 +8820,31 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>通所リハビリテーション</t>
+          <t>介護予防訪問入浴介護</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>日/月</t>
+          <t>回/月</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>153</v>
-      </c>
-      <c r="H46" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr"/>
@@ -8347,17 +8854,17 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D47" s="14" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="G47" s="14" t="n">
-        <v>24.2</v>
+      <c r="D47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H47" s="9" t="inlineStr"/>
     </row>
@@ -8369,25 +8876,25 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>短期入所生活介護</t>
+          <t>介護予防訪問看護</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>日/月</t>
+          <t>回/月</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H48" s="9" t="inlineStr"/>
     </row>
@@ -8399,17 +8906,17 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D49" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G49" s="14" t="n">
-        <v>0.4</v>
+      <c r="D49" s="13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>5.5</v>
       </c>
       <c r="H49" s="9" t="inlineStr"/>
     </row>
@@ -8421,12 +8928,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（介護老人保健施設）</t>
+          <t>介護予防訪問リハビリテーション</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>日/月</t>
+          <t>回/月</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
@@ -8441,7 +8948,11 @@
       <c r="G50" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="9" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr"/>
@@ -8451,17 +8962,17 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D51" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G51" s="14" t="n">
-        <v>0.1</v>
+      <c r="D51" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="inlineStr"/>
     </row>
@@ -8473,7 +8984,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（病院等）</t>
+          <t>介護予防居宅療養管理指導</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -8481,23 +8992,19 @@
           <t>人/月</t>
         </is>
       </c>
-      <c r="D52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
+      <c r="D52" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -8507,59 +9014,47 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>短期入所療養介護（介護医療院）</t>
+          <t>介護予防通所リハビリテーション</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>153</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr"/>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>福祉用具貸与</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="G54" s="14" t="n">
-        <v>51.9</v>
+      <c r="D54" s="13" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>24.2</v>
       </c>
       <c r="H54" s="9" t="inlineStr"/>
     </row>
@@ -8571,55 +9066,47 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>特定福祉用具販売</t>
+          <t>介護予防短期入所生活介護</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr"/>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D55" s="14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E55" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F55" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G55" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H55" s="9" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>住宅改修</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="14" t="n">
-        <v>1</v>
+      <c r="D56" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>0.4</v>
       </c>
       <c r="H56" s="9" t="inlineStr"/>
     </row>
@@ -8631,170 +9118,483 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護</t>
+          <t>介護予防短期入所療養介護（介護老人保健施設）</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr"/>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="9" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>居宅</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>居宅介護支援・介護予防支援</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="G58" s="14" t="n">
-        <v>69.09999999999999</v>
+      <c r="D58" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>0.1</v>
       </c>
       <c r="H58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>地域密着型</t>
+          <t>居宅</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護</t>
+          <t>介護予防短期入所療養介護（病院等）</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr"/>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>月報に実績なし。人数のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>地域密着型</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>小規模多機能型居宅介護</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>人/月</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="G60" s="14" t="n">
-        <v>6.7</v>
+      <c r="D60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>介護予防短期入所療養介護（介護医療院）</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr"/>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>介護予防福祉用具貸与</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="H63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>特定介護予防福祉用具販売</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>介護予防住宅改修</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>介護予防特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>居宅</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>介護予防支援</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="E67" s="13" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
           <t>地域密着型</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>介護予防認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>日/月</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>**月報に実績がない。量は0**</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr"/>
+      <c r="B69" s="6" t="inlineStr"/>
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>人/月</t>
         </is>
       </c>
-      <c r="D61" s="14" t="n">
+      <c r="D69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>介護予防小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E70" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>介護予防認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="E61" s="14" t="n">
+      <c r="E71" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="F61" s="14" t="n">
+      <c r="F71" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="G61" s="14" t="n">
+      <c r="G71" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="H61" s="9" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>予防給付　利用者数の合計</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr"/>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>人/月</t>
+        </is>
+      </c>
+      <c r="D72" s="21" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="E72" s="21" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="F72" s="21" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="G72" s="21" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t>延べ利用者数。重複を含む</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>※ 計画書の見込量表にそのまま載せられる形にしたもの。回・日で表記するサービスは、量と人数の2行で示している。</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
         <is>
           <t>**※ 訪問系の「回/月」は国保連月報の実日数による。**計画書に載せる前に、回数として表記してよいかを町と確認する。</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
         <is>
           <t>**※ 令和7年度（実績）は、量が国保連月報の実測日数÷12、人数が年報の件数÷12である。**出所が異なるため、量÷人数は1件当たり日数と厳密には一致しない（件数が年報628件 対 月報642件で2.2％違う）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>※ サービス名は計画書の正式名称による（予防給付は「介護予防」を冠する）。</t>
         </is>
       </c>
     </row>
@@ -8804,6 +9604,475 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>町内定員</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>R11見込（人/月）</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>R11見込（1日あたり）</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>充足率</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="n">
+        <v>54</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>67.57309661483505</v>
+      </c>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="24" t="n">
+        <v>125.1353641015464</v>
+      </c>
+      <c r="H2" s="15" t="inlineStr">
+        <is>
+          <t>**超過**</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>町外の事業所の利用による。自給率の分析と整合させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>29.40970410640422</v>
+      </c>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="26" t="n"/>
+      <c r="H3" s="27" t="inlineStr">
+        <is>
+          <t>町内になし</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>町外の事業所の利用による。見込量は残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>1.15819537225288</v>
+      </c>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>町内になし</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>町外の事業所の利用による。見込量は残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設入所者生活介護</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>58</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>43.16949712507921</v>
+      </c>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="28" t="n">
+        <v>74.43016745703312</v>
+      </c>
+      <c r="H5" s="27" t="inlineStr">
+        <is>
+          <t>余力あり</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>定員は上限として働いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>98</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>50.2039949457116</v>
+      </c>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="28" t="n">
+        <v>51.22856627113429</v>
+      </c>
+      <c r="H6" s="27" t="inlineStr">
+        <is>
+          <t>余力あり</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>定員は上限として働いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>3.496975399239993</v>
+      </c>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="26" t="n"/>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>町内になし</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>町外の事業所の利用による。見込量は残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>通所系</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>通所介護</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>139</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>人/日</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>176.4562509710697</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>59.71704903722409</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>42.96190578217561</v>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
+        <is>
+          <t>余力あり</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>定員は上限として働いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>通所系</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>通所リハビリテーション</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>人/日</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>48.96160292407099</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>12.25727585744368</v>
+      </c>
+      <c r="G9" s="26" t="n"/>
+      <c r="H9" s="27" t="inlineStr">
+        <is>
+          <t>町内になし</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>町外の事業所の利用による。見込量は残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>通所系</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>人/日</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>8.362886476289001</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>3.040286822650884</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>25.3357235220907</v>
+      </c>
+      <c r="H10" s="27" t="inlineStr">
+        <is>
+          <t>余力あり</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>定員は上限として働いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>通所系</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>人/日（通い）</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>31.26553562615783</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>19.62871031041987</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>65.42903436806623</v>
+      </c>
+      <c r="H11" s="27" t="inlineStr">
+        <is>
+          <t>余力あり</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>定員は上限として働いていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>※ 定員は見える化システムのＤ25〜Ｄ27（令和7年度）による。出典は介護サービス情報公表システム。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>※ 通所系は、見込延べ日数を月26日の営業日で割って1日あたりの利用者数にしている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>**※ 介護老人福祉施設は町内定員54人に対し見込み67.6人/月で、13.6人が町外の施設の利用にあたる。**第9期の自給率の分析と整合させる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**※ 小規模多機能型居宅介護は登録定員が29人以下と定められている。**見込み31.3人/月は登録者数にあたるため、1事業所であれば上限を超える。事業所数と登録定員を町に確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>※ 認知症対応型共同生活介護の定員は令和5年度71人から令和6年度98人へ増えている。第9期が「新規整備を原則行わない」方針であったこととの整合を、第9期評価で整理する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8873,13 +10142,13 @@
           <t>令和6年度　月報の3区分計 対 年報 様式2 総計（給付額・円）</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="23" t="n">
         <v>1075154636</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="23" t="n">
         <v>1085998383</v>
       </c>
-      <c r="E2" s="20" t="n">
+      <c r="E2" s="23" t="n">
         <v>-10843747</v>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -8887,7 +10156,7 @@
           <t>-1.00％</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
@@ -8907,13 +10176,13 @@
           <t>令和7年度　月報の3区分計 対 年報 様式2 総計（給付額・円）</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="23" t="n">
         <v>995045765</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="23" t="n">
         <v>1005144062</v>
       </c>
-      <c r="E3" s="20" t="n">
+      <c r="E3" s="23" t="n">
         <v>-10098297</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -8921,7 +10190,7 @@
           <t>-1.00％</t>
         </is>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
@@ -8941,13 +10210,13 @@
           <t>令和7年度 件数の合計　年報 対 月報（介護給付）</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="23" t="n">
         <v>12295</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="23" t="n">
         <v>12275</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="23" t="n">
         <v>20</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -8955,7 +10224,7 @@
           <t>+0.16％</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>
@@ -8975,13 +10244,13 @@
           <t>令和7年度 件数の合計　年報 対 月報（予防給付）</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="23" t="n">
         <v>2193</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="23" t="n">
         <v>2183</v>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="23" t="n">
         <v>10</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -8989,7 +10258,7 @@
           <t>+0.46％</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>軽微</t>
         </is>

--- a/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_回数日数ベース見込量_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/04_算定・見込量/小野町_第10期_回数日数ベース見込量_20260914.xlsx
@@ -5757,37 +5757,37 @@
         <v>250242.1508379888</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>254789.1248438966</v>
+        <v>250242.1508379888</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>+1.8％</t>
+          <t>-0.0％</t>
         </is>
       </c>
       <c r="J23" s="13" t="n">
-        <v>48.25028634922224</v>
+        <v>44.6850130699971</v>
       </c>
       <c r="K23" s="14" t="n"/>
       <c r="L23" s="7" t="n">
-        <v>147523.778788629</v>
+        <v>134184.8853703166</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>48.10994229352351</v>
+        <v>44.55503920999129</v>
       </c>
       <c r="N23" s="14" t="n"/>
       <c r="O23" s="7" t="n">
-        <v>147094.6811190867</v>
+        <v>133794.5861109497</v>
       </c>
       <c r="P23" s="13" t="n">
-        <v>47.96959823782478</v>
+        <v>44.42506534998548</v>
       </c>
       <c r="Q23" s="14" t="n"/>
       <c r="R23" s="7" t="n">
-        <v>146665.5834495444</v>
+        <v>133404.2868515829</v>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
-          <t>+7.2％</t>
+          <t>-0.7％</t>
         </is>
       </c>
       <c r="T23" s="9" t="inlineStr"/>
@@ -7030,37 +7030,37 @@
         <v>8721.492732558139</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>8305.223344467251</v>
+        <v>8721.492732558139</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>-4.8％</t>
+          <t>+0.0％</t>
         </is>
       </c>
       <c r="J11" s="13" t="n">
-        <v>52.21991636898127</v>
+        <v>57.25007261109497</v>
       </c>
       <c r="K11" s="14" t="n"/>
       <c r="L11" s="7" t="n">
-        <v>5204.376821685491</v>
+        <v>5991.673106593087</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>52.06802597814654</v>
+        <v>57.08355116661826</v>
       </c>
       <c r="N11" s="14" t="n"/>
       <c r="O11" s="7" t="n">
-        <v>5189.23901824836</v>
+        <v>5974.245319779262</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>51.91613558731181</v>
+        <v>56.91702972214154</v>
       </c>
       <c r="Q11" s="14" t="n"/>
       <c r="R11" s="7" t="n">
-        <v>5174.10121481123</v>
+        <v>5956.817532965438</v>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>-9.4％</t>
+          <t>-0.7％</t>
         </is>
       </c>
       <c r="T11" s="9" t="inlineStr"/>
@@ -7440,17 +7440,17 @@
       <c r="T17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>地域密着型</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>介護予防認知症対応型共同生活介護</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>人</t>
         </is>
@@ -7464,44 +7464,40 @@
         <v>238812.4285714286</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>232517.0685324384</v>
-      </c>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>-2.6％</t>
+        <v>238812.4285714286</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>-0.0％</t>
         </is>
       </c>
       <c r="J18" s="13" t="n">
-        <v>2.247471001086859</v>
+        <v>1.164972407783909</v>
       </c>
       <c r="K18" s="14" t="n"/>
       <c r="L18" s="7" t="n">
-        <v>6270.904425412573</v>
+        <v>3338.51867905896</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>2.240933854486839</v>
+        <v>1.161583890018395</v>
       </c>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="7" t="n">
-        <v>6252.664447444531</v>
+        <v>3328.808037176881</v>
       </c>
       <c r="P18" s="13" t="n">
-        <v>2.234396707886819</v>
+        <v>1.15819537225288</v>
       </c>
       <c r="Q18" s="14" t="n"/>
       <c r="R18" s="7" t="n">
-        <v>6234.42446947649</v>
-      </c>
-      <c r="S18" s="15" t="inlineStr">
-        <is>
-          <t>+91.5％</t>
-        </is>
-      </c>
-      <c r="T18" s="16" t="inlineStr">
-        <is>
-          <t>**令和7年度実績から15％を超えて動く。基準期間を令和5〜7年度の3年平均としているため、一方向に動いてきたサービスでは平均に引き戻される。00シートの「趨勢のあるサービスの扱い」を参照**</t>
-        </is>
-      </c>
+        <v>3319.097395294801</v>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>-0.7％</t>
+        </is>
+      </c>
+      <c r="T18" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -8548,13 +8544,13 @@
         <v>44.8</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>48.3</v>
+        <v>44.7</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>48.1</v>
+        <v>44.6</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>48</v>
+        <v>44.4</v>
       </c>
       <c r="H36" s="9" t="inlineStr"/>
     </row>
@@ -8784,13 +8780,13 @@
         <v>1024.6</v>
       </c>
       <c r="E44" s="21" t="n">
-        <v>1055.3</v>
+        <v>1051.7</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>1052.2</v>
+        <v>1048.7</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>1049.2</v>
+        <v>1045.6</v>
       </c>
       <c r="H44" s="22" t="inlineStr">
         <is>
@@ -9294,13 +9290,13 @@
         <v>57.3</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>52.2</v>
+        <v>57.3</v>
       </c>
       <c r="F63" s="13" t="n">
-        <v>52.1</v>
+        <v>57.1</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>51.9</v>
+        <v>56.9</v>
       </c>
       <c r="H63" s="9" t="inlineStr"/>
     </row>
@@ -9530,13 +9526,13 @@
         <v>1.2</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="F71" s="13" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="H71" s="9" t="inlineStr"/>
     </row>
@@ -9556,13 +9552,13 @@
         <v>182.8</v>
       </c>
       <c r="E72" s="21" t="n">
-        <v>165.3</v>
+        <v>169.3</v>
       </c>
       <c r="F72" s="21" t="n">
-        <v>164.8</v>
+        <v>168.8</v>
       </c>
       <c r="G72" s="21" t="n">
-        <v>164.4</v>
+        <v>168.3</v>
       </c>
       <c r="H72" s="22" t="inlineStr">
         <is>
@@ -9830,11 +9826,11 @@
         </is>
       </c>
       <c r="E6" s="13" t="n">
-        <v>50.2039949457116</v>
+        <v>45.58326072223836</v>
       </c>
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="28" t="n">
-        <v>51.22856627113429</v>
+        <v>46.51353134922282</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
